--- a/AAII_Financials/Quarterly/SCHW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCHW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>SCHW</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7072000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6482000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6336000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6135000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5851000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5599000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5329000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4847000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4690000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4740000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4556000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4606000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4559000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5213000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6309000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5931000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5259000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4808000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4836000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4693000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4648000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4819000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4272000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2537000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2547000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2753000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2774000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2972000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2999000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3040000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2957000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2807000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2669000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2556000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2361000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2204000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2136000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2017000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1955000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E9" s="3">
         <v>163000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>142000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>149000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>176000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>153000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>131000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>147000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>172000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>141000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>144000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>151000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>188000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>146000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>812000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>431000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>166000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>136000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>128000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>123000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>121000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>104000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>96000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>89000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>97000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>136000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>168000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>261000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>318000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>317000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>288000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>228000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>183000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>158000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>119000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>94000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>74000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>55000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>45000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>46000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6874000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6319000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6194000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5986000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5675000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5446000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5198000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4700000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4518000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4599000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4412000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4455000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4371000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5067000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5497000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5500000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5093000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4672000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4708000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4570000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4527000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4715000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>4176000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2448000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2450000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2617000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2606000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2711000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2681000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2723000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2669000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2579000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2486000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2398000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2242000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2165000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2130000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2081000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1972000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1909000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,77 +1467,80 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E14" s="3">
         <v>11000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-32000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>76000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>20000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>45000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>31000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>544000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>376000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>22000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>194000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>99000</v>
       </c>
       <c r="R14" s="3">
         <v>99000</v>
       </c>
       <c r="S14" s="3">
+        <v>99000</v>
+      </c>
+      <c r="T14" s="3">
         <v>92000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>91000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>98000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>141000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>115000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1537,8 +1556,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1573,130 +1592,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>333000</v>
+        <v>340000</v>
       </c>
       <c r="E15" s="3">
         <v>333000</v>
       </c>
       <c r="F15" s="3">
+        <v>333000</v>
+      </c>
+      <c r="G15" s="3">
         <v>339000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>343000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>347000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>348000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>353000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>357000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>358000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>368000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>333000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>325000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>312000</v>
       </c>
       <c r="Q15" s="3">
         <v>312000</v>
       </c>
       <c r="R15" s="3">
+        <v>312000</v>
+      </c>
+      <c r="S15" s="3">
         <v>319000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>313000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>304000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>299000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>293000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>289000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>283000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>277000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>122000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>109000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>96000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>94000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>88000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>84000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>83000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>80000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>78000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>73000</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>69000</v>
       </c>
       <c r="AL15" s="3">
         <v>69000</v>
       </c>
       <c r="AM15" s="3">
+        <v>69000</v>
+      </c>
+      <c r="AN15" s="3">
         <v>66000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>65000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>61000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3375000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3283000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3188000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3114000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3048000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3144000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2948000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2985000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2898000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2911000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2818000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2847000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2846000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2909000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3711000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3254000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2985000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2969000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2813000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2682000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2929000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2859000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2796000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1648000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1659000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1706000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1662000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1736000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1763000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1776000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1747000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1588000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1538000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1554000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1408000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1314000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1295000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1293000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1193000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1161000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3697000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3199000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3148000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3021000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2803000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2455000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2381000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1862000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1792000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1829000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1738000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1759000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1713000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2304000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2598000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2677000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2274000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1839000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2023000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2011000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1719000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1960000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1476000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>889000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>888000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1047000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1112000</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>1236000</v>
       </c>
       <c r="AE18" s="3">
         <v>1236000</v>
       </c>
       <c r="AF18" s="3">
+        <v>1236000</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1264000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1210000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1219000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1131000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1002000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>953000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>945000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>909000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>843000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>824000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>794000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,8 +2101,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2146,130 +2179,136 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4037000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3532000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3481000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3360000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3146000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2802000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2729000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2215000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2149000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2187000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2106000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2092000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2038000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2616000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2910000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2996000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2587000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2143000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2322000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2304000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2008000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2243000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1753000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1011000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>997000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1143000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1206000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1324000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1320000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1347000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1290000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1297000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1206000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1075000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1022000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1014000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>975000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>908000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>885000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>854000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3669000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3188000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3180000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3021000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2803000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2455000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2305000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1842000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1747000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1798000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1194000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1383000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1691000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2110000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2598000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2677000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2274000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1839000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2023000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2011000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1719000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1960000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1476000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>889000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>888000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1047000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1112000</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>1236000</v>
       </c>
       <c r="AE23" s="3">
         <v>1236000</v>
       </c>
       <c r="AF23" s="3">
+        <v>1236000</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1264000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1210000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1219000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1131000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1002000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>953000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>945000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>909000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>843000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>824000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>794000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>869000</v>
+      </c>
+      <c r="E24" s="3">
         <v>709000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>721000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>663000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>677000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>546000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>465000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>434000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>415000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>436000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>149000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>258000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>397000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>507000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>630000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>657000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>481000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>437000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>443000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>485000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>454000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>476000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>341000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>191000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>217000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>252000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>260000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>285000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>299000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>275000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>296000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>265000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>219000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>310000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>327000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>334000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>279000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>302000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>291000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2479000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2459000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2358000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2126000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1909000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1840000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1408000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1332000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1362000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1045000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1125000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1294000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1603000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1968000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2020000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1793000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1402000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1580000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1526000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1265000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1484000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1135000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>698000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>671000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>795000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>852000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>951000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>937000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>964000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>935000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>923000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>866000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>783000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>643000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>618000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>575000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>564000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>522000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2681000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2397000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2367500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2277000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1977000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1796000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1717400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1299000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1211000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1251000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>926000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1017000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1173000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1533000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1821000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1884000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1652000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1278000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1449000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1406000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1117000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1388000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1050000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>615000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>621000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>757000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>801000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>913000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>887000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>925000</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>885000</v>
       </c>
       <c r="AH27" s="3">
         <v>885000</v>
       </c>
       <c r="AI27" s="3">
+        <v>885000</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>813000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>746000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>596000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>575000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>530000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>525000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>478000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>470000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-46000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,8 +3601,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2479000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2459000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2358000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2126000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1909000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1840000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1408000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1332000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1362000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1045000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1125000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1294000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1603000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1821000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1884000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1652000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1278000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1449000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1406000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1117000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1388000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1050000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>615000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>621000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>757000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>801000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>913000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>887000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>925000</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>885000</v>
       </c>
       <c r="AH33" s="3">
         <v>885000</v>
       </c>
       <c r="AI33" s="3">
+        <v>885000</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>813000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>746000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>550000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>575000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>530000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>525000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>478000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>470000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2479000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2459000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2358000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2126000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1909000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1840000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1408000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1332000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1362000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1045000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1125000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1294000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1603000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1821000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1884000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1652000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1278000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1449000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1406000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1117000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1388000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1050000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>615000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>621000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>757000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>801000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>913000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>887000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>925000</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>885000</v>
       </c>
       <c r="AH35" s="3">
         <v>885000</v>
       </c>
       <c r="AI35" s="3">
+        <v>885000</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>813000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>746000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>550000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>575000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>530000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>525000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>478000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>470000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40580000</v>
+      </c>
+      <c r="E41" s="3">
         <v>44975000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46030000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30572000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32195000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>35009000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42083000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34850000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25350000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31752000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>43337000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33251000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47651000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49162000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>40195000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46486000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>64550000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>91126000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>62975000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>34323000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30337000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>48182000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>40348000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27465000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>33574000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>68458000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>29345000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20252000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24199000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32558000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>27938000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>21830000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13250000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14145000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>14217000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>12253000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>9575000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>9475000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>10828000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>10431000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>55776000</v>
+      </c>
+      <c r="E42" s="3">
         <v>51500000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>50890000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>53109000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>49916000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41474000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>41459000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37421000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25347000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>29902000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>35312000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>19471000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>26433000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>32135000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,130 +4524,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>194567000</v>
+      </c>
+      <c r="E43" s="3">
         <v>172019000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>168681000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>151349000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>137414000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>135504000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>135451000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>118870000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>116603000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>113517000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>114246000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>110891000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>106719000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>104527000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>66591000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>73966000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>76213000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>84134000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>90565000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>86607000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>82295000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>74757000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>64440000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>25441000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>21421000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>19001000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>21767000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>22386000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>21891000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21145000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>22204000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>23209000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>23376000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>22047000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>21225000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>19126000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>18903000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>17450000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>17883000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>17327000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,8 +4774,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4711,30 +4809,30 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>100000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>99000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>348000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1438000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
+      <c r="R45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
         <v>16576000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4744,11 +4842,11 @@
       <c r="W45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
+      <c r="X45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
@@ -4756,98 +4854,101 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3">
         <v>17265000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>11455000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6457000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6012000</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3">
         <v>6368000</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>5621000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>8389000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>8543000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>8686000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>10895000</v>
       </c>
-      <c r="AN45" s="3">
-        <v>0</v>
-      </c>
       <c r="AO45" s="3">
         <v>0</v>
       </c>
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>290923000</v>
+      </c>
+      <c r="E46" s="3">
         <v>268494000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>265601000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>235030000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>219525000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>211987000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>218993000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>191141000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>167300000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>175171000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>192995000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>163712000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>181151000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>187262000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,335 +5024,344 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>190788000</v>
+      </c>
+      <c r="E47" s="3">
         <v>191710000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>197843000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>198675000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>203756000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>214308000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>226431000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>241763000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>248558000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>257457000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>268585000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>275557000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>294617000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>312443000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>376299000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>387444000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>423178000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>429205000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>438423000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>422814000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>402112000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>381446000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>376696000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>340112000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>311840000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>258385000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>223724000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>224114000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>218609000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>216632000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>234930000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>217998000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>214799000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>198833000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>194534000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>186344000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>177109000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>174671000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>168420000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>157563000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3659000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3065000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3796000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3136000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3197000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3276000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3929000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3340000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3436000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3584000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4320000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3730000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3686000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3716000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4608000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3687000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3670000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3499000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4284000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3164000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3136000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3054000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2883000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2346000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2314000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2291000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2705000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2613000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2510000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2410000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1769000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1683000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1599000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1540000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1471000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1392000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1335000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1305000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1299000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1266000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19573000</v>
+      </c>
+      <c r="E49" s="3">
         <v>19711000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19184000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19311000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19438000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19566000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19694000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19824000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19954000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20082000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20211000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20341000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20475000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20610000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20740000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20874000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>21026000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>21179000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>21331000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>21484000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>21638000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>21790000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>21943000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2995000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3011000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1227000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1355000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>1227000</v>
       </c>
       <c r="AE49" s="3">
         <v>1227000</v>
@@ -5266,31 +5376,34 @@
         <v>1227000</v>
       </c>
       <c r="AI49" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>1320000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1328000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1335000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1342000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1352000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1362000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1371000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1381000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,88 +5649,91 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12323000</v>
+      </c>
+      <c r="E52" s="3">
         <v>10339000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2024000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9103000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13020000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13766000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6782000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9987000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10427000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12490000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2351000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11864000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11576000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11521000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30824000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30474000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>19276000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>40434000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>40853000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>28675000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26945000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>27006000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>35495000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>15868000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>23781000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -5623,17 +5742,17 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
         <v>7063000</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
-      </c>
       <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
         <v>4063000</v>
       </c>
-      <c r="AI52" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
@@ -5647,16 +5766,19 @@
         <v>0</v>
       </c>
       <c r="AN52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3">
         <v>21481000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>22174000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>20077000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>517266000</v>
+      </c>
+      <c r="E54" s="3">
         <v>493319000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>490995000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>465255000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>458936000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>462903000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>479843000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>466055000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>449675000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>468784000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>493178000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>475204000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>511505000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>535552000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>551772000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>577563000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>637557000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>680950000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>667270000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>607548000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>574532000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>563457000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>549009000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>419355000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>400484000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>370779000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>294005000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>278987000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>276321000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>282815000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>296482000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>272102000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>261882000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>248320000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>243274000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>230714000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>220601000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>227061000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>223383000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>209337000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,419 +6116,429 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>129135000</v>
+      </c>
+      <c r="E57" s="3">
         <v>119609000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>116899000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>116114000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>110301000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101662000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>101827000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>89164000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>79966000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>84005000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>86037000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>72818000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>84795000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>87553000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>97438000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>110012000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>114880000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>125307000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>125671000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>113052000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>105012000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>101339000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>104201000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>52006000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>50135000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>49251000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>39220000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>37358000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>35635000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>31303000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>34557000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>29373000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>33666000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>32210000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>32530000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>36907000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>34973000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>36910000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>38301000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>36458000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54116000</v>
+      </c>
+      <c r="E58" s="3">
         <v>41489000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>38243000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>33181000</v>
       </c>
-      <c r="G58" s="3">
-        <v>38211000</v>
-      </c>
       <c r="H58" s="3">
+        <v>35123000</v>
+      </c>
+      <c r="I58" s="3">
         <v>35939000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>37992000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>47887000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>41996000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>39556000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>42000000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>45228000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>53443000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>56838000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>383774000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>396215000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>443353000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>470061000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>448633000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>398275000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>372138000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>372398000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>358022000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>320717000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>301566000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>277477000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>220094000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>209327000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>208375000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>219454000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>231423000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>213408000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>199922000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>190184000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>184656000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>170263000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>162600000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>167489000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>163454000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>152631000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>249682000</v>
+      </c>
+      <c r="E59" s="3">
         <v>253041000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>255747000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>239057000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>233058000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>246160000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>259121000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>246462000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>252420000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>269460000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>289953000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>284408000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>304414000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>325745000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13124000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13451000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13699000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15611000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>17791000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>19249000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21224000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16428000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>17094000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7465000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9442000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9259000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5516000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3521000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3567000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3604000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2954000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2697000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2408000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2468000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2810000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2249000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2021000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2162000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2331000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1902000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>444100000</v>
+      </c>
+      <c r="E60" s="3">
         <v>424982000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>421542000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>398663000</v>
       </c>
-      <c r="G60" s="3">
-        <v>391386000</v>
-      </c>
       <c r="H60" s="3">
+        <v>388298000</v>
+      </c>
+      <c r="I60" s="3">
         <v>393799000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>409368000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>397685000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>384551000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>404088000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>427678000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>411816000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>451124000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>478521000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21659000</v>
+      </c>
+      <c r="E61" s="3">
         <v>17969000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18754000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16099000</v>
       </c>
-      <c r="G61" s="3">
-        <v>17108000</v>
-      </c>
       <c r="H61" s="3">
+        <v>20196000</v>
+      </c>
+      <c r="I61" s="3">
         <v>18621000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21019000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20217000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20224000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21490000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23370000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24803000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22482000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20016000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20828000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20844000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21112000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21873000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18914000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>19530000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18708000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>17698000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13632000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7836000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8526000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8522000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7430000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7427000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7424000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6829000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>6878000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5790000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5789000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4128000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4753000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3268000</v>
-      </c>
-      <c r="AM61" s="3">
-        <v>3518000</v>
       </c>
       <c r="AN61" s="3">
         <v>3518000</v>
       </c>
       <c r="AO61" s="3">
-        <v>2876000</v>
+        <v>3518000</v>
       </c>
       <c r="AP61" s="3">
         <v>2876000</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>2876000</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1360000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1134000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1111000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1109000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>991000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>972000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>947000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>938000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>947000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>794000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1047000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>801000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>752000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>668000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>467119000</v>
+      </c>
+      <c r="E66" s="3">
         <v>444085000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>441570000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>415871000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>409485000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>413392000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>431468000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>418840000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>405722000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>426372000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>452220000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>437420000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>474358000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>499205000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>515164000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>540522000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>593044000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>632852000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>611009000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>550106000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>517082000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>507863000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>492949000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>388024000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>369669000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>344509000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>272260000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>257633000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>255001000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>261190000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>275812000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>251268000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>241785000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>228990000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>224749000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>212687000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>203112000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>210079000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>206962000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>193867000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,13 +7659,16 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>6763000</v>
+        <v>6213000</v>
       </c>
       <c r="E70" s="3">
         <v>6763000</v>
@@ -7513,7 +7680,7 @@
         <v>6763000</v>
       </c>
       <c r="H70" s="3">
-        <v>9191000</v>
+        <v>6763000</v>
       </c>
       <c r="I70" s="3">
         <v>9191000</v>
@@ -7540,19 +7707,19 @@
         <v>9191000</v>
       </c>
       <c r="Q70" s="3">
+        <v>9191000</v>
+      </c>
+      <c r="R70" s="3">
         <v>9706000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>10297000</v>
-      </c>
-      <c r="S70" s="3">
-        <v>10694000</v>
       </c>
       <c r="T70" s="3">
         <v>10694000</v>
       </c>
       <c r="U70" s="3">
-        <v>9954000</v>
+        <v>10694000</v>
       </c>
       <c r="V70" s="3">
         <v>9954000</v>
@@ -7561,19 +7728,19 @@
         <v>9954000</v>
       </c>
       <c r="X70" s="3">
+        <v>9954000</v>
+      </c>
+      <c r="Y70" s="3">
         <v>10539000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>7733000</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>5263000</v>
       </c>
       <c r="AA70" s="3">
         <v>5263000</v>
       </c>
       <c r="AB70" s="3">
-        <v>2793000</v>
+        <v>5263000</v>
       </c>
       <c r="AC70" s="3">
         <v>2793000</v>
@@ -7603,7 +7770,7 @@
         <v>2793000</v>
       </c>
       <c r="AL70" s="3">
-        <v>2783000</v>
+        <v>2793000</v>
       </c>
       <c r="AM70" s="3">
         <v>2783000</v>
@@ -7615,10 +7782,13 @@
         <v>2783000</v>
       </c>
       <c r="AP70" s="3">
+        <v>2783000</v>
+      </c>
+      <c r="AQ70" s="3">
         <v>2192000</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>48044000</v>
+      </c>
+      <c r="E72" s="3">
         <v>45912000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44065000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>42170000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>40374000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>38882000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>37568000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>36303000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>35458000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>34701000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33901000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>33429000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>32865000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>32144000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31066000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>29651000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>28174000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>26895000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>25992000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>24880000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>23809000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>23029000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>21975000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21261000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>20876000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>20487000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19960000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19374000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18680000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18017000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>17329000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16615000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>15903000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15222000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>14408000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13963000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13495000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13069000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>12649000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>12261000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43934000</v>
+      </c>
+      <c r="E76" s="3">
         <v>42471000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42662000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42621000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42688000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>40320000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>39184000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>38024000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34762000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>33221000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31767000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28593000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27956000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27156000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26902000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26744000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>33819000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>37404000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46307000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47488000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>47496000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>45055000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>48327000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>26068000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>25552000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23477000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18952000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18561000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18527000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18832000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17877000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18041000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17304000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>16537000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15732000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15244000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14706000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14199000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>13638000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>13278000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2479000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2459000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2358000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2126000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1909000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1840000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1408000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1332000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1362000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1045000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1125000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1294000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1603000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1821000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1884000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1652000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1278000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1449000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1406000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1117000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1388000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1050000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>615000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>621000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>757000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>801000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>913000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>887000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>925000</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>885000</v>
       </c>
       <c r="AH81" s="3">
         <v>885000</v>
       </c>
       <c r="AI81" s="3">
+        <v>885000</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>813000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>746000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>550000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>575000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>530000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>525000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>478000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>470000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E83" s="3">
         <v>217000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>237000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>218000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>233000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>228000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>238000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>198000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>191000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>177000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>176000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>167000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>159000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>150000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>312000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>319000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>313000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>304000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>299000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>293000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>289000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>283000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>277000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>122000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>109000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>96000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>94000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>88000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>84000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>83000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>80000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>78000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>73000</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>69000</v>
       </c>
       <c r="AL83" s="3">
         <v>69000</v>
       </c>
       <c r="AM83" s="3">
+        <v>69000</v>
+      </c>
+      <c r="AN83" s="3">
         <v>66000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>65000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>61000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>60000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4300000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7342000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-763000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>538000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3177000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6359000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10827000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19098000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4252000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1349000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>20037000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5011000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5216000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9777000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2107000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9054000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7943000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3053000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5639000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1815000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-594000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4742000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13257000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-80000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-16443000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10118000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4304000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5402000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2214000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2595000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7801000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1275000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3132000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>248000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1188000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1942000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>843000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-334000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1688000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-549000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-140000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-158000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-145000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-128000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-117000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-254000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-128000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-89000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-149000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-63000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-239000</v>
       </c>
       <c r="O91" s="3">
         <v>-239000</v>
       </c>
       <c r="P91" s="3">
+        <v>-239000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-202000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-232000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-241000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-296000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-313000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-178000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-239000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-186000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-166000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-130000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-179000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-156000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-193000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-205000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-171000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-139000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-170000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-147000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-131000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-122000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-133000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-103000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-84000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-74000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-77000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6414000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1151000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6143000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>9076000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10470000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7734000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>8516000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>9706000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9475000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>9682000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>18533000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>18167000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>11029000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>11540000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>21760000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2390000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3642000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-21693000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22951000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17861000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13158000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22406000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-26000000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-58249000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19196000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1295000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7189000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2163000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>18285000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-14535000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6366000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-13115000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6539000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-13242000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-5914000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>4270000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-5587000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-12731000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-12210000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E96" s="3">
         <v>562000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>481000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>492000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>493000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>492000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>459000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>460000</v>
       </c>
       <c r="K96" s="3">
         <v>460000</v>
       </c>
       <c r="L96" s="3">
-        <v>459000</v>
+        <v>460000</v>
       </c>
       <c r="M96" s="3">
         <v>459000</v>
       </c>
       <c r="N96" s="3">
-        <v>458000</v>
+        <v>459000</v>
       </c>
       <c r="O96" s="3">
         <v>458000</v>
       </c>
       <c r="P96" s="3">
+        <v>458000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>463000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-420000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-416000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-378000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-391000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-328000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-356000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-327000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-355000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-326000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-248000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-247000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-206000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-243000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-208000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-242000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-161000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-191000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-170000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-184000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-136000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-163000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-135000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-121000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-135000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1964000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3713000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16710000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7385000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18665000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20362000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1604000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7726000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16012000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-24926000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-153000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-27722000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23274000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10096000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15959000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-49394000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-27979000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>24609000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>49291000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>26507000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-254000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>20779000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>41347000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>18129000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>26298000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>58208000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>10284000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-111000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-11883000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-12229000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>17867000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>13267000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>11276000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>4756000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>15771000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>7273000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5013000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>4568000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>11440000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>10214000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4078000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3619000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14796000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-704000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6412000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3533000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1489000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19888000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10558000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16800000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29566000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14200000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10323000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10710000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6526000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18580000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-33532000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>24020000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33237000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5371000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-18709000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2879000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32198000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7951000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-48394000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>49130000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13293000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1898000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-7506000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3461000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>11133000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8176000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1293000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1535000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1341000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3301000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>100000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1353000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>397000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-2545000</v>
       </c>
     </row>
